--- a/public/file/gaji/Penggajian-ARIMBI-Bulan-1-2020.xlsx
+++ b/public/file/gaji/Penggajian-ARIMBI-Bulan-1-2020.xlsx
@@ -564,491 +564,491 @@
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:32">
-      <c r="A1" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="0" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:32">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="0">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+      <c r="D2" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="0">
+        <v>1</v>
+      </c>
+      <c r="G2" s="0">
         <v>2020</v>
       </c>
     </row>
     <row r="3" spans="1:32">
-      <c r="A3">
+      <c r="A3" s="0">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="E3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
+      <c r="E3" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="0">
+        <v>1</v>
+      </c>
+      <c r="G3" s="0">
         <v>2020</v>
       </c>
     </row>
     <row r="4" spans="1:32">
-      <c r="A4">
+      <c r="A4" s="0">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
+      <c r="D4" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="0">
+        <v>1</v>
+      </c>
+      <c r="G4" s="0">
         <v>2020</v>
       </c>
     </row>
     <row r="5" spans="1:32">
-      <c r="A5">
+      <c r="A5" s="0">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="E5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
+      <c r="E5" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="0">
+        <v>1</v>
+      </c>
+      <c r="G5" s="0">
         <v>2020</v>
       </c>
     </row>
     <row r="6" spans="1:32">
-      <c r="A6">
+      <c r="A6" s="0">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
+      <c r="D6" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="0">
+        <v>1</v>
+      </c>
+      <c r="G6" s="0">
         <v>2020</v>
       </c>
     </row>
     <row r="7" spans="1:32">
-      <c r="A7">
+      <c r="A7" s="0">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
+      <c r="D7" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="0">
+        <v>1</v>
+      </c>
+      <c r="G7" s="0">
         <v>2020</v>
       </c>
     </row>
     <row r="8" spans="1:32">
-      <c r="A8">
+      <c r="A8" s="0">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
+      <c r="D8" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="0">
+        <v>1</v>
+      </c>
+      <c r="G8" s="0">
         <v>2020</v>
       </c>
     </row>
     <row r="9" spans="1:32">
-      <c r="A9">
+      <c r="A9" s="0">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="D9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
+      <c r="D9" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="0">
+        <v>1</v>
+      </c>
+      <c r="G9" s="0">
         <v>2020</v>
       </c>
     </row>
     <row r="10" spans="1:32">
-      <c r="A10">
+      <c r="A10" s="0">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
+      <c r="D10" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="0">
+        <v>1</v>
+      </c>
+      <c r="G10" s="0">
         <v>2020</v>
       </c>
     </row>
     <row r="11" spans="1:32">
-      <c r="A11">
+      <c r="A11" s="0">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="D11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
+      <c r="D11" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="0">
+        <v>1</v>
+      </c>
+      <c r="G11" s="0">
         <v>2020</v>
       </c>
     </row>
     <row r="12" spans="1:32">
-      <c r="A12">
+      <c r="A12" s="0">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="D12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
+      <c r="D12" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="0">
+        <v>1</v>
+      </c>
+      <c r="G12" s="0">
         <v>2020</v>
       </c>
     </row>
     <row r="13" spans="1:32">
-      <c r="A13">
+      <c r="A13" s="0">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="D13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
+      <c r="D13" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="0">
+        <v>1</v>
+      </c>
+      <c r="G13" s="0">
         <v>2020</v>
       </c>
     </row>
     <row r="14" spans="1:32">
-      <c r="A14">
+      <c r="A14" s="0">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="D14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
+      <c r="D14" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="0">
+        <v>1</v>
+      </c>
+      <c r="G14" s="0">
         <v>2020</v>
       </c>
     </row>
     <row r="15" spans="1:32">
-      <c r="A15">
+      <c r="A15" s="0">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="D15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
+      <c r="D15" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="0">
+        <v>1</v>
+      </c>
+      <c r="G15" s="0">
         <v>2020</v>
       </c>
     </row>
     <row r="16" spans="1:32">
-      <c r="A16">
+      <c r="A16" s="0">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D16" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
+      <c r="D16" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="0">
+        <v>1</v>
+      </c>
+      <c r="G16" s="0">
         <v>2020</v>
       </c>
     </row>
     <row r="17" spans="1:32">
-      <c r="A17">
+      <c r="A17" s="0">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="D17" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17">
+      <c r="D17" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="0">
+        <v>1</v>
+      </c>
+      <c r="G17" s="0">
         <v>2020</v>
       </c>
     </row>
     <row r="18" spans="1:32">
-      <c r="A18">
+      <c r="A18" s="0">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18">
+      <c r="D18" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="0">
+        <v>1</v>
+      </c>
+      <c r="G18" s="0">
         <v>2020</v>
       </c>
     </row>
